--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129700507</v>
       </c>
       <c r="B2" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96004</v>
+        <v>96005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96005</v>
+        <v>96010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96010</v>
+        <v>96014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96014</v>
+        <v>96016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96016</v>
+        <v>96026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129700507</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96026</v>
+        <v>96030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129700507</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96030</v>
+        <v>96033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96033</v>
+        <v>96034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96034</v>
+        <v>96051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129700507</v>
+        <v>129700100</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>308661</v>
+        <v>308670</v>
       </c>
       <c r="R2" t="n">
-        <v>6423857</v>
+        <v>6423944</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>129700401</v>
       </c>
       <c r="B3" t="n">
-        <v>96056</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,6 +886,327 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129700439</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lokullemossen, Lokullemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>308673</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6423874</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129700307</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lokullemossen, Lokullemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>308670</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6423944</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129700507</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lokullemossen, Lokullemossen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>308661</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6423857</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Solberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53007-2025 artfynd.xlsx
+++ b/artfynd/A 53007-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700439</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700307</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,8 +1232,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>